--- a/Script_5_single_factor_pathway/region_vs_region_GSEA/Supplementary_table_region_vs_reigon_single_factor_GSEA.xlsx
+++ b/Script_5_single_factor_pathway/region_vs_region_GSEA/Supplementary_table_region_vs_reigon_single_factor_GSEA.xlsx
@@ -1,30 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/outobi/Downloads/final analysis/single factor/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/outobi/Downloads/final analysis/final code/Script_5_single_factor_pathway/region_vs_region_GSEA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63AA2804-E51C-0544-9A96-99BB12FEFD98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD1F7C4F-8064-574E-82E5-187C3C78F35C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4060" yWindow="3160" windowWidth="27240" windowHeight="16440" firstSheet="2" activeTab="9" xr2:uid="{D5BAC588-A04A-2545-A7AC-5EE0BDE63D5D}"/>
+    <workbookView xWindow="39120" yWindow="2120" windowWidth="27240" windowHeight="16440" firstSheet="1" activeTab="8" xr2:uid="{D5BAC588-A04A-2545-A7AC-5EE0BDE63D5D}"/>
   </bookViews>
   <sheets>
-    <sheet name="GO bottom vs central" sheetId="1" r:id="rId1"/>
-    <sheet name="Reactome bottom vs central" sheetId="2" r:id="rId2"/>
-    <sheet name="GO bottom vs peri" sheetId="3" r:id="rId3"/>
-    <sheet name="Reactome bottom vs peri" sheetId="4" r:id="rId4"/>
-    <sheet name="GO central vs top" sheetId="6" r:id="rId5"/>
-    <sheet name="Reactome central vs top" sheetId="7" r:id="rId6"/>
-    <sheet name="Reactome top vs central" sheetId="10" r:id="rId7"/>
-    <sheet name="GO top vs peri" sheetId="8" r:id="rId8"/>
-    <sheet name="GO peri vs top" sheetId="11" r:id="rId9"/>
-    <sheet name="Reactome peri vs top" sheetId="9" r:id="rId10"/>
+    <sheet name="GO bottom &lt; central" sheetId="1" r:id="rId1"/>
+    <sheet name="Reactome bottom &lt; central" sheetId="2" r:id="rId2"/>
+    <sheet name="GO bottom &lt; peri" sheetId="3" r:id="rId3"/>
+    <sheet name="GO central &gt; top" sheetId="6" r:id="rId4"/>
+    <sheet name="Reactome central &gt; top" sheetId="7" r:id="rId5"/>
+    <sheet name="Reactome central &lt; top" sheetId="10" r:id="rId6"/>
+    <sheet name="GO peri &lt; top" sheetId="8" r:id="rId7"/>
+    <sheet name="GO peri &gt; top" sheetId="11" r:id="rId8"/>
+    <sheet name="Reactome peri &lt; top" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,6 +35,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -1669,75 +1669,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0E5FDDD-EC22-9E40-9A28-7EBD863E3AA8}">
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2">
-        <v>14</v>
-      </c>
-      <c r="D2">
-        <v>6</v>
-      </c>
-      <c r="E2">
-        <v>-0.93005000000000004</v>
-      </c>
-      <c r="F2">
-        <v>-2.0954999999999999</v>
-      </c>
-      <c r="G2" s="4">
-        <v>2.2E-16</v>
-      </c>
-      <c r="H2">
-        <v>1.8949000000000001E-2</v>
-      </c>
-      <c r="I2">
-        <f>-LOG10(H2)</f>
-        <v>1.7224137042152368</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49E0F21A-0A35-B247-BA76-840338D5D9B5}">
   <dimension ref="A1:I10"/>
@@ -2288,15 +2219,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF691A8E-0E7E-AE41-84E6-2752AFFDB378}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18F37902-4A75-8F48-A30F-5B90E5250442}">
   <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -2841,7 +2763,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E73CA282-D8DA-8E4B-B694-94D16DB3788D}">
   <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -3093,7 +3015,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41874B5E-5117-A74B-8AF4-35A2705319F8}">
   <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -3315,7 +3237,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{523E033A-0F74-8942-A7A4-93E45C5623B4}">
   <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -3418,7 +3340,7 @@
         <v>2.2E-16</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3:J15" si="0">-LOG10(I3)</f>
+        <f t="shared" ref="J3:J14" si="0">-LOG10(I3)</f>
         <v>15.657577319177793</v>
       </c>
     </row>
@@ -3790,7 +3712,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F2296F-3135-8A48-9161-4D0CDCD7B5C9}">
   <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -3856,8 +3778,77 @@
         <v>2.2218000000000002E-2</v>
       </c>
       <c r="J2">
-        <f t="shared" ref="J1:J2" si="0">-LOG10(I2)</f>
+        <f t="shared" ref="J2" si="0">-LOG10(I2)</f>
         <v>1.6532950375669138</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0E5FDDD-EC22-9E40-9A28-7EBD863E3AA8}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2">
+        <v>14</v>
+      </c>
+      <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>-0.93005000000000004</v>
+      </c>
+      <c r="F2">
+        <v>-2.0954999999999999</v>
+      </c>
+      <c r="G2" s="4">
+        <v>2.2E-16</v>
+      </c>
+      <c r="H2">
+        <v>1.8949000000000001E-2</v>
+      </c>
+      <c r="I2">
+        <f>-LOG10(H2)</f>
+        <v>1.7224137042152368</v>
       </c>
     </row>
   </sheetData>
